--- a/input_data/LV_Database.xlsx
+++ b/input_data/LV_Database.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jan-Steffen Fischer\Desktop\LEAT_to_update\input_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jan-Steffen Fischer\Desktop\Testi\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BBC4879-0C0C-4446-90F1-50B2EF8EFC61}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77EEEE45-97EE-4F33-AF64-D1D63BE9694F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LV_Database" sheetId="1" r:id="rId1"/>
@@ -21,11 +21,24 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">LV_Database!$A$1:$BM$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="162">
   <si>
     <t>sheet: LV_Database</t>
   </si>
@@ -490,6 +503,27 @@
   </si>
   <si>
     <t>d_exit</t>
+  </si>
+  <si>
+    <t>engine_cycle</t>
+  </si>
+  <si>
+    <t>mf_oc</t>
+  </si>
+  <si>
+    <t>rof_oc</t>
+  </si>
+  <si>
+    <t>Ae/At_oc</t>
+  </si>
+  <si>
+    <t>p_chamber_oc</t>
+  </si>
+  <si>
+    <t>GG</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
 </sst>
 </file>
@@ -973,7 +1007,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1187,13 +1221,45 @@
     </xf>
     <xf numFmtId="3" fontId="2" fillId="2" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Link" xfId="1" builtinId="8"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2811,17 +2877,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6" style="29" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.5546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5546875" style="29" customWidth="1"/>
-    <col min="5" max="5" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="10.5546875" style="29" customWidth="1"/>
+    <col min="10" max="10" width="25.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>51</v>
       </c>
@@ -2834,11 +2900,26 @@
       <c r="D1" s="75" t="s">
         <v>154</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="75" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" s="75" t="s">
+        <v>156</v>
+      </c>
+      <c r="G1" s="75" t="s">
+        <v>157</v>
+      </c>
+      <c r="H1" s="75" t="s">
+        <v>158</v>
+      </c>
+      <c r="I1" s="75" t="s">
+        <v>159</v>
+      </c>
+      <c r="J1" s="26" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -2851,11 +2932,18 @@
       <c r="D2" s="2">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2868,11 +2956,18 @@
       <c r="D3" s="28">
         <v>2</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>55</v>
       </c>
@@ -2885,11 +2980,18 @@
       <c r="D4" s="2">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -2902,11 +3004,18 @@
       <c r="D5" s="2">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>59</v>
       </c>
@@ -2919,11 +3028,18 @@
       <c r="D6" s="2">
         <v>2</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -2936,11 +3052,18 @@
       <c r="D7" s="2">
         <v>2</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -2953,11 +3076,26 @@
       <c r="D8" s="2">
         <v>2</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="76">
+        <v>4.2767106842737095E-2</v>
+      </c>
+      <c r="G8" s="76">
+        <v>0.3</v>
+      </c>
+      <c r="H8" s="76">
+        <v>1.23</v>
+      </c>
+      <c r="I8" s="76">
+        <v>200</v>
+      </c>
+      <c r="J8" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>65</v>
       </c>
@@ -2970,11 +3108,26 @@
       <c r="D9" s="2">
         <v>2</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F9" s="76">
+        <v>4.2767106842737095E-2</v>
+      </c>
+      <c r="G9" s="76">
+        <v>0.3</v>
+      </c>
+      <c r="H9" s="76">
+        <v>1.23</v>
+      </c>
+      <c r="I9" s="76">
+        <v>200</v>
+      </c>
+      <c r="J9" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -2987,11 +3140,18 @@
       <c r="D10" s="2">
         <v>2</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>69</v>
       </c>
@@ -3004,11 +3164,18 @@
       <c r="D11" s="2">
         <v>2</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -3021,11 +3188,18 @@
       <c r="D12" s="2">
         <v>2</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>131</v>
       </c>
@@ -3038,8 +3212,11 @@
       <c r="D13" s="29">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E13" s="29" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>132</v>
       </c>
@@ -3052,8 +3229,15 @@
       <c r="D14" s="65">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E14" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>133</v>
       </c>
@@ -3066,8 +3250,27 @@
       <c r="D15" s="29">
         <v>2</v>
       </c>
+      <c r="E15" s="29" t="s">
+        <v>161</v>
+      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F9:I9">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="2" priority="4">
+      <formula>LEN(TRIM(F9))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F8:I8">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="containsBlanks" dxfId="0" priority="2">
+      <formula>LEN(TRIM(F8))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
